--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/PENNSYLVANIA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/PENNSYLVANIA_2018.xlsx
@@ -3894,7 +3894,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C197">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C510">
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C528">
@@ -11029,7 +11029,7 @@
         <v>51</v>
       </c>
       <c r="D593">
-        <v>0.009766373037150517</v>
+        <v>0.009766373037150515</v>
       </c>
     </row>
     <row r="594">
@@ -12937,7 +12937,7 @@
         <v>51</v>
       </c>
       <c r="D699">
-        <v>0.009766373037150517</v>
+        <v>0.009766373037150515</v>
       </c>
     </row>
     <row r="700">
